--- a/naver-place-crawler/results_health/파주_PT.xlsx
+++ b/naver-place-crawler/results_health/파주_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>파이 피트니스 다율점</t>
+          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pifitness02@naver.com</t>
+          <t>pifitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1436-5392</t>
+          <t>0507-1350-3458</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 파주시 해올2길 8 1006~1009호(다율동)</t>
+          <t>경기도 파주시 경의로1240번길 14-11 8층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sWflSZei</t>
+          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whg35h5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>476</v>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>2322</v>
       </c>
       <c r="R2" t="n">
-        <v>91</v>
+        <v>2798</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2076933270</t>
+          <t>1448948729</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076933270</t>
+          <t>https://m.place.naver.com/place/1448948729</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리바디피티스튜디오</t>
+          <t>파이 피트니스 다율점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rebody7530@naver.com</t>
+          <t>pifitness02@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1331-7549</t>
+          <t>0507-1436-5392</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1114 505호</t>
+          <t>경기도 파주시 해올2길 8 1006~1009호(다율동)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_body_pt?igsh=MWFmcWk5OGp6ZWNyMQ==</t>
+          <t>https://open.kakao.com/o/sWflSZei</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,17 +700,13 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjtwmo7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="R3" t="n">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2037075259</t>
+          <t>2076933270</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037075259</t>
+          <t>https://m.place.naver.com/place/2076933270</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,25 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>힙디자인팩토리PT 운정본점</t>
+          <t>리바디피티스튜디오</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hipdesignfactory@naver.com</t>
+          <t>rebody7530@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1331-7549</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 파주시 가람로116번길 45 4층</t>
+          <t>경기도 파주시 경의로 1114 505호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/hipupup</t>
+          <t>https://www.instagram.com/re_body_pt?igsh=MWFmcWk5OGp6ZWNyMQ==</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1700</v>
+        <v>28</v>
       </c>
       <c r="R4" t="n">
-        <v>1834</v>
+        <v>62</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1455989939</t>
+          <t>2037075259</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1455989939</t>
+          <t>https://m.place.naver.com/place/2037075259</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -867,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1246 유은타워 8차 10층 짐원휘트니스 운정9호점</t>
+          <t>경기도 파주시 경의로 1246 유은타워 8차 10층 짐원휘트니스 운정9호점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -892,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5jxu34</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q5" t="n">
         <v>155</v>
       </c>
       <c r="R5" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -936,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -961,7 +953,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 파주시 해올2길 21 월드타워 19차 4층</t>
+          <t>경기도 파주시 해올2길 21 월드타워 19차 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,14 +978,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ei58</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1008,10 +996,10 @@
         <v>246</v>
       </c>
       <c r="Q6" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="R6" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1030,7 +1018,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1030,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐원휘트니스 여성전용 가람8호점 헬스PT</t>
+          <t>힙디자인팩토리PT 운정본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gymonelab@naver.com</t>
+          <t>hipdesignfactory@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1055,12 +1043,12 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 파주시 가람로 67 한양프라자 2층</t>
+          <t>경기도 파주시 가람로116번길 45 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymonelab</t>
+          <t>https://smartstore.naver.com/hipupup</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,19 +1063,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpv77pv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,17 +1079,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="Q7" t="n">
-        <v>390</v>
+        <v>1723</v>
       </c>
       <c r="R7" t="n">
-        <v>474</v>
+        <v>1857</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,51 +1098,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1553794151</t>
+          <t>1455989939</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1553794151</t>
+          <t>https://m.place.naver.com/place/1455989939</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
+          <t>로드짐 야당점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pifitness@naver.com</t>
+          <t>roadgym86@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1350-3458</t>
+          <t>0507-1458-6779</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1240번길 14-11 8층</t>
+          <t>경기도 파주시 경의로1004번길 33 3층 303호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
+          <t>https://www.instagram.com/road_gym_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1173,22 +1157,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wl490ee</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1197,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>458</v>
+        <v>81</v>
       </c>
       <c r="Q8" t="n">
-        <v>2902</v>
+        <v>116</v>
       </c>
       <c r="R8" t="n">
-        <v>3360</v>
+        <v>197</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1448948729</t>
+          <t>1959563259</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448948729</t>
+          <t>https://m.place.naver.com/place/1959563259</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1234,39 +1214,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
+          <t>F45 운정</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1percentgym2@naver.com</t>
+          <t>f45unjeong@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1386-4598</t>
+          <t>0507-1391-6365</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 파주시 금빛로 4-1 3층 301호,302호</t>
+          <t>경기도 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
+          <t>https://www.instagram.com/f45_unjeong</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1276,14 +1256,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yr9z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>388</v>
+        <v>132</v>
       </c>
       <c r="Q9" t="n">
-        <v>267</v>
+        <v>420</v>
       </c>
       <c r="R9" t="n">
-        <v>655</v>
+        <v>552</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,51 +1286,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1714420485</t>
+          <t>1564837926</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1714420485</t>
+          <t>https://m.place.naver.com/place/1564837926</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>애블바디PT 초롱꽃마을 2호점 헬스PT</t>
+          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>every_body_pt@naver.com</t>
+          <t>1percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1427-5294</t>
+          <t>0507-1386-4598</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 파주시 양지로 117 304호,305호</t>
+          <t>경기도 파주시 금빛로 4-1 3층 301호,302호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/</t>
+          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1364,7 +1340,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1374,14 +1350,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdljl0j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1389,17 +1361,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>389</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>267</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>656</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2038397745</t>
+          <t>1714420485</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038397745</t>
+          <t>https://m.place.naver.com/place/1714420485</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1402,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>애블바디PT 해오름마을 1호점 헬스PT</t>
+          <t>애블바디PT 초롱꽃마을 2호점 헬스PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1441,13 +1413,13 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1362-5290</t>
+          <t>0507-1427-5294</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 파주시 해올2길 16 공감빌딩 6층 애블바디 P.T샵</t>
+          <t>경기도 파주시 양지로 117 304호,305호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1472,14 +1444,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44dez</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>272</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>421</v>
+        <v>7</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,17 +1474,111 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>2038397745</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038397745</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>애블바디PT 해오름마을 1호점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>every_body_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1362-5290</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 파주시 해올2길 16 공감빌딩 6층 애블바디 P.T샵</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>275</v>
+      </c>
+      <c r="R12" t="n">
+        <v>422</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>1831911897</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1831911897</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/파주_PT.xlsx
+++ b/naver-place-crawler/results_health/파주_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1240번길 14-11 8층</t>
+          <t>경기도 파주시 경의로1240번길 14-11 8층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wl490ee</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Q2" t="n">
         <v>2323</v>
       </c>
       <c r="R2" t="n">
-        <v>2804</v>
+        <v>2805</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 파주시 해올2길 8 1006~1009호(다율동)</t>
+          <t>경기도 파주시 해올2길 8 1006~1009호(다율동)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whg35h5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1114 505호</t>
+          <t>경기도 파주시 경의로 1114 505호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjtwmo7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1246 유은타워 8차 10층 짐원휘트니스 운정9호점</t>
+          <t>경기도 파주시 경의로 1246 유은타워 8차 10층 짐원휘트니스 운정9호점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5jxu34</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -969,7 +953,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 파주시 해올2길 21 월드타워 19차 4층</t>
+          <t>경기도 파주시 해올2길 21 월드타워 19차 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +978,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ei58</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1050,25 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>힙디자인팩토리PT 운정본점</t>
+          <t>로드짐 야당점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hipdesignfactory@naver.com</t>
+          <t>roadgym86@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1458-6779</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 파주시 가람로116번길 45 4층</t>
+          <t>경기도 파주시 경의로1004번길 33 3층 303호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/hipupup</t>
+          <t>https://www.instagram.com/road_gym_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1103,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="Q7" t="n">
-        <v>1729</v>
+        <v>116</v>
       </c>
       <c r="R7" t="n">
-        <v>1863</v>
+        <v>197</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1455989939</t>
+          <t>1959563259</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1455989939</t>
+          <t>https://m.place.naver.com/place/1959563259</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,29 +1124,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>로드짐 야당점</t>
+          <t>힙디자인팩토리PT 운정본점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>roadgym86@naver.com</t>
+          <t>hipdesignfactory@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1458-6779</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1004번길 33 3층 303호</t>
+          <t>경기도 파주시 가람로116번길 45 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/road_gym_</t>
+          <t>https://smartstore.naver.com/hipupup</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1182,14 +1162,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44xex</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1201,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="Q8" t="n">
-        <v>116</v>
+        <v>1731</v>
       </c>
       <c r="R8" t="n">
-        <v>197</v>
+        <v>1865</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1192,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1959563259</t>
+          <t>1455989939</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1959563259</t>
+          <t>https://m.place.naver.com/place/1455989939</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1255,7 +1231,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
+          <t>경기도 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1280,14 +1256,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zxi6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1336,56 +1308,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>다다짐 헬스&amp;PT 운정본점</t>
+          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dadagym@naver.com</t>
+          <t>1percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-1646</t>
+          <t>0507-1386-4598</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 파주시 미래로602번길 11 701호,702호</t>
+          <t>경기도 파주시 금빛로 4-1 3층 301호,302호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dadagym/224242550028</t>
+          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4v2ogs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1397,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>59</v>
+        <v>387</v>
       </c>
       <c r="Q10" t="n">
-        <v>70</v>
+        <v>267</v>
       </c>
       <c r="R10" t="n">
-        <v>129</v>
+        <v>654</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1236035000</t>
+          <t>1714420485</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236035000</t>
+          <t>https://m.place.naver.com/place/1714420485</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1429,34 +1397,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
+          <t>애블바디PT 초롱꽃마을 2호점 헬스PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1percentgym2@naver.com</t>
+          <t>every_body_pt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1386-4598</t>
+          <t>0507-1427-5294</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 파주시 금빛로 4-1 3층 301호,302호</t>
+          <t>경기도 파주시 양지로 117 304호,305호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1466,7 +1434,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1476,14 +1444,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yr9z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,17 +1455,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>387</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>267</v>
+        <v>33</v>
       </c>
       <c r="R11" t="n">
-        <v>654</v>
+        <v>36</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,113 +1474,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1714420485</t>
+          <t>2038397745</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1714420485</t>
+          <t>https://m.place.naver.com/place/2038397745</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>애블바디PT 초롱꽃마을 2호점 헬스PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>every_body_pt@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1427-5294</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 파주시 양지로 117 304호,305호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://smartstore.naver.com/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdljl0j</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2038397745</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2038397745</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/파주_PT.xlsx
+++ b/naver-place-crawler/results_health/파주_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리바디피티스튜디오</t>
+          <t>파이 피트니스 다율점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rebody7530@naver.com</t>
+          <t>pifitness02@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1331-7549</t>
+          <t>0507-1436-5392</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1114 505호</t>
+          <t>경기도 파주시 해올2길 8 1006~1009호(다율동)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_body_pt?igsh=MWFmcWk5OGp6ZWNyMQ==</t>
+          <t>https://open.kakao.com/o/sWflSZei</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="R2" t="n">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2037075259</t>
+          <t>2076933270</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037075259</t>
+          <t>https://m.place.naver.com/place/2076933270</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>리바디피티스튜디오</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>rebody7530@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1331-7549</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기 파주시 경의로 1114 505호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>https://www.instagram.com/re_body_pt?igsh=MWFmcWk5OGp6ZWNyMQ==</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +695,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjtwmo7</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1221</v>
+        <v>35</v>
       </c>
       <c r="Q3" t="n">
-        <v>1612</v>
+        <v>28</v>
       </c>
       <c r="R3" t="n">
-        <v>2833</v>
+        <v>63</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>2037075259</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/2037075259</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -931,34 +935,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
+          <t>로드짐 야당점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pifitness@naver.com</t>
+          <t>roadgym86@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1350-3458</t>
+          <t>0507-1458-6779</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로1240번길 14-11 8층</t>
+          <t>경기도 파주시 경의로1004번길 33 3층 303호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
+          <t>https://www.instagram.com/road_gym_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -973,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -984,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="Q6" t="n">
-        <v>2324</v>
+        <v>116</v>
       </c>
       <c r="R6" t="n">
-        <v>2807</v>
+        <v>197</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1448948729</t>
+          <t>1959563259</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448948729</t>
+          <t>https://m.place.naver.com/place/1959563259</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1025,34 +1029,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>로드짐 야당점</t>
+          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>roadgym86@naver.com</t>
+          <t>pifitness@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1458-6779</t>
+          <t>0507-1350-3458</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로1004번길 33 3층 303호</t>
+          <t>경기도 파주시 경의로1240번길 14-11 8층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/road_gym_</t>
+          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1067,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1078,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>81</v>
+        <v>483</v>
       </c>
       <c r="Q7" t="n">
-        <v>116</v>
+        <v>2325</v>
       </c>
       <c r="R7" t="n">
-        <v>197</v>
+        <v>2808</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1959563259</t>
+          <t>1448948729</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1959563259</t>
+          <t>https://m.place.naver.com/place/1448948729</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1180,10 +1184,10 @@
         <v>134</v>
       </c>
       <c r="Q8" t="n">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="R8" t="n">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1308,44 +1312,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>다다짐 헬스&amp;PT 운정본점</t>
+          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dadagym@naver.com</t>
+          <t>1percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-1646</t>
+          <t>0507-1386-4598</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 파주시 미래로602번길 11 701호,702호</t>
+          <t>경기도 파주시 금빛로 4-1 3층 301호,302호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dadagym/224242550028</t>
+          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>59</v>
+        <v>387</v>
       </c>
       <c r="Q10" t="n">
-        <v>70</v>
+        <v>267</v>
       </c>
       <c r="R10" t="n">
-        <v>129</v>
+        <v>654</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1236035000</t>
+          <t>1714420485</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236035000</t>
+          <t>https://m.place.naver.com/place/1714420485</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,7 +1406,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>애블바디PT 해오름마을 1호점 헬스PT</t>
+          <t>애블바디PT 초롱꽃마을 2호점 헬스PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1413,13 +1417,13 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1362-5290</t>
+          <t>0507-1427-5294</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 파주시 해올2길 16 공감빌딩 6층 애블바디 P.T샵</t>
+          <t>경기 파주시 양지로 117 304호,305호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1444,10 +1448,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdljl0j</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>148</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>276</v>
+        <v>33</v>
       </c>
       <c r="R11" t="n">
-        <v>424</v>
+        <v>36</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1831911897</t>
+          <t>2038397745</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1831911897</t>
+          <t>https://m.place.naver.com/place/2038397745</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1491,34 +1499,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>더 블랙 피트니스</t>
+          <t>애블바디PT 해오름마을 1호점 헬스PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>theblack_fitness@naver.com</t>
+          <t>every_body_pt@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1341-6432</t>
+          <t>0507-1362-5290</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 파주시 청석로 260 트리플메디칼타워 4층 더 블랙 피트니스</t>
+          <t>경기도 파주시 해올2길 16 공감빌딩 6층 애블바디 P.T샵</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://litt.ly/theblack_fitness</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1549,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="Q12" t="n">
-        <v>28</v>
+        <v>276</v>
       </c>
       <c r="R12" t="n">
-        <v>80</v>
+        <v>424</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1340211997</t>
+          <t>1831911897</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340211997</t>
+          <t>https://m.place.naver.com/place/1831911897</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1590,29 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>올마이티짐 헬스&amp;PT</t>
+          <t>더 블랙 피트니스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>almg-yadang@naver.com</t>
+          <t>theblack_fitness@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1460-1270</t>
+          <t>0507-1341-6432</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1042 7층 올마이티짐</t>
+          <t>경기 파주시 청석로 260 트리플메디칼타워 4층 더 블랙 피트니스</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xbxlxnGn</t>
+          <t>https://litt.ly/theblack_fitness</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1632,13 +1640,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wvjoz2r</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1647,13 +1659,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>715</v>
+        <v>52</v>
       </c>
       <c r="Q13" t="n">
-        <v>283</v>
+        <v>28</v>
       </c>
       <c r="R13" t="n">
-        <v>998</v>
+        <v>80</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,12 +1674,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1141836591</t>
+          <t>1340211997</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141836591</t>
+          <t>https://m.place.naver.com/place/1340211997</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">

--- a/naver-place-crawler/results_health/파주_PT.xlsx
+++ b/naver-place-crawler/results_health/파주_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1524,6 +1524,198 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1percentgym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1386-4598</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기 파주시 금빛로 4-1 3층 301호,302호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yr9z</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>387</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>267</v>
+      </c>
+      <c r="R12" t="n">
+        <v>654</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1714420485</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1714420485</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>애블바디PT 초롱꽃마을 2호점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>every_body_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1427-5294</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 파주시 양지로 117 304호,305호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>33</v>
+      </c>
+      <c r="R13" t="n">
+        <v>36</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2038397745</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038397745</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
